--- a/data/trans_orig/Q20C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q20C_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007 (tasa de respuesta: 96,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,81%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>878</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012 (tasa de respuesta: 97,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13181</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10761</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,2%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>20091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19485</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,55%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>960</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13866</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>30731</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>44475</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>22331</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>39277</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>63987</t>
+          <t>64152</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016 (tasa de respuesta: 92,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,49%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -9849,12 +9849,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>68,37%</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -11443,12 +11443,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11160</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>48,73%</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -12012,12 +12012,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -12125,12 +12125,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -12238,12 +12238,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>965</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023 (tasa de respuesta: 93,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13384,12 +13384,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,71%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13645,12 +13645,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13695,12 +13695,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>65,5%</t>
         </is>
       </c>
     </row>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -13953,12 +13953,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -14066,12 +14066,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14136,12 +14136,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,89%</t>
         </is>
       </c>
     </row>
@@ -14179,12 +14179,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14377,12 +14377,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -14522,12 +14522,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14537,12 +14537,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14572,12 +14572,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14592,12 +14592,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -14640,7 +14640,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>460</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14720,12 +14720,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -14748,12 +14748,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11161</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>529</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15141,12 +15141,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15161,12 +15161,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15176,12 +15176,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15204,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>831</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,66%</t>
         </is>
       </c>
     </row>
@@ -15317,12 +15317,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>367</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15332,12 +15332,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15387,12 +15387,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15402,12 +15402,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15495,17 +15495,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -15608,17 +15608,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15660,12 +15660,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15675,12 +15675,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15695,12 +15695,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>834</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15710,12 +15710,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15730,12 +15730,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15745,12 +15745,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,2%</t>
         </is>
       </c>
     </row>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>534</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>824</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15936,12 +15936,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15956,12 +15956,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15971,12 +15971,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -16229,12 +16229,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -16342,12 +16342,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>74,91%</t>
         </is>
       </c>
     </row>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16470,12 +16470,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16510,7 +16510,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -16568,12 +16568,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>355</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>357</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -16798,12 +16798,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16833,12 +16833,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>31240</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24436</t>
+          <t>24749</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26872</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -17137,12 +17137,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>23740</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17187,12 +17187,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>49151</t>
+          <t>49389</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q20C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q20C_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,27%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,23%</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9149</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>865</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>22150</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19041</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>47277</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>820</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,28%</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,94%</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21035</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11757</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20091</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18557</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>30575</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>44475</t>
+          <t>44613</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36333</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>21795</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>43399</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>40272</t>
+          <t>39948</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>64152</t>
+          <t>63035</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>994</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>54,87%</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>63,52%</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,95%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>66,13%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,82 +10546,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>63,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>61,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>7261</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2999</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>861</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>7326</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14148</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,95%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -11478,12 +11478,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>9673</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24998</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39251</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>42242</t>
+          <t>41987</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -13379,32 +13379,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -13424,12 +13424,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13449,32 +13449,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -13605,32 +13605,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13675,32 +13675,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>
@@ -13718,32 +13718,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13753,27 +13753,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -13788,32 +13788,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -13831,17 +13831,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13866,17 +13866,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>590</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -13993,12 +13993,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>590</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -14028,12 +14028,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -14061,32 +14061,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14096,32 +14096,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14131,32 +14131,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -14174,32 +14174,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>472</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -14219,12 +14219,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14244,32 +14244,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14322,32 +14322,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14357,32 +14357,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -14400,17 +14400,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14435,17 +14435,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14517,32 +14517,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14552,32 +14552,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14587,32 +14587,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>653</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14700,32 +14700,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>436</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -14743,32 +14743,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>626</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -14788,12 +14788,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14813,32 +14813,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -14856,32 +14856,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -14901,12 +14901,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14926,32 +14926,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>57,76%</t>
         </is>
       </c>
     </row>
@@ -14969,17 +14969,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15004,17 +15004,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -15096,12 +15096,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15121,32 +15121,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -15171,17 +15171,17 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -15199,32 +15199,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15234,32 +15234,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15269,32 +15269,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -15312,32 +15312,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15347,32 +15347,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>518</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15382,32 +15382,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -15425,32 +15425,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15460,32 +15460,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15495,32 +15495,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13571</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -15538,17 +15538,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15573,17 +15573,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15655,32 +15655,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15690,32 +15690,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15725,32 +15725,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>845</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -15778,12 +15778,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15803,32 +15803,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15838,32 +15838,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15916,32 +15916,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15951,32 +15951,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -15994,32 +15994,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16029,32 +16029,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16064,32 +16064,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>58,22%</t>
         </is>
       </c>
     </row>
@@ -16107,17 +16107,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16142,17 +16142,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12817</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12817</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12817</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16177,17 +16177,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>349</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>856</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -16304,12 +16304,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -16372,32 +16372,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16407,32 +16407,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,5%</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -16510,7 +16510,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -16530,12 +16530,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -16598,32 +16598,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>409</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16633,32 +16633,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>410</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -16676,17 +16676,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16711,17 +16711,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16746,17 +16746,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16793,32 +16793,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16828,32 +16828,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16863,32 +16863,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>22711</t>
+          <t>27579</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>36990</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -16906,32 +16906,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16941,32 +16941,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16976,32 +16976,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12418</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -17019,32 +17019,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17054,32 +17054,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17089,32 +17089,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>26872</t>
+          <t>29861</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -17132,32 +17132,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29300</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17167,32 +17167,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>18776</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>26361</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17202,32 +17202,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>40419</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>32305</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>49389</t>
+          <t>53305</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -17245,17 +17245,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17280,17 +17280,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>42021</t>
+          <t>48847</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>42021</t>
+          <t>48847</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>42021</t>
+          <t>48847</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17315,17 +17315,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>98753</t>
+          <t>111403</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>98753</t>
+          <t>111403</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>98753</t>
+          <t>111403</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
